--- a/experiment/Wavlet_bestx4/Test/results_table.xlsx
+++ b/experiment/Wavlet_bestx4/Test/results_table.xlsx
@@ -570,38 +570,38 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>31.826/
-0.8869</t>
+          <t>31.928/
+0.8893</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>28.420/
-0.7759</t>
+          <t>28.471/
+0.7779</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>27.435/
-0.7313</t>
+          <t>27.482/
+0.7334</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>25.682/
-0.7709</t>
+          <t>25.808/
+0.7757</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>29.790/
-0.8962</t>
+          <t>29.998/
+0.9002</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>28.631/
-0.8122</t>
+          <t>28.737/
+0.8153</t>
         </is>
       </c>
     </row>

--- a/experiment/Wavlet_bestx4/Test/results_table.xlsx
+++ b/experiment/Wavlet_bestx4/Test/results_table.xlsx
@@ -565,7 +565,7 @@
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">
-5,454K</t>
+2,280K</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
